--- a/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
@@ -597,7 +597,9 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
+          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+https://file.go.gov.sg/nais2023.pdf
+https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -624,14 +626,13 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>NAIS 2.0 = dic-2023; el Update de may-2026 (10 prioridades refrescadas) se cuenta como estrategia vigente nueva (decisión del operador 2026-06-16) → tramo 2024-25.  [confianza: ALTA · decisión operador]
-Nota matriz: EE: White Paper 2024-30 · SG: Update NAIS may-2026 = estrategia vigente (decisión operador) · DE: Aktionsplan 2023 · ES: Estrategia 2024 · PT: ANIA 2026-30</t>
+          <t>NAIS 2.0 = dic-2023; el Update de may-2026 (10 prioridades refrescadas) se cuenta como estrategia vigente nueva (decisión del operador 2026-06-16) → tramo 2024-25.  [confianza: ALTA · decisión operador]</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://www.mddi.gov.sg/newsroom/04122023/
-https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/</t>
+          <t>https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -663,7 +664,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/</t>
+          <t>https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-6191</t>
         </is>
       </c>
     </row>
@@ -695,7 +697,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
+          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
@@ -722,13 +725,13 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>'More than S$1 billion' en 5 años.  [confianza: ALTA]
-Nota matriz: EE €85M · SG &gt;S$1.000M · DE €5.000M · ES €1.500M · PT &gt;€400M</t>
+          <t>'More than S$1 billion' en 5 años.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf</t>
+          <t>https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf
+https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -760,7 +763,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -825,7 +829,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -890,7 +895,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://www.pdpc.gov.sg</t>
         </is>
       </c>
     </row>
@@ -954,7 +960,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -986,7 +993,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://aisingapore.org/</t>
         </is>
       </c>
     </row>
@@ -1046,8 +1054,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>NO se halló componente de género con plan → 0.  [confianza: MEDIA · NO ENCONTRADO]
-Nota matriz: Solo ES recoge género (mención transversal); resto NO ENCONTRADO/0</t>
+          <t>NO se halló componente de género con plan → 0.  [confianza: MEDIA · NO ENCONTRADO]</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1079,8 +1086,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>'Green AI'; Sustainable Tropical Data Centre Testbed.  [confianza: MEDIA · PRELIM]
-Nota matriz: PT: solo principio en EDN, no eje en ANIA</t>
+          <t>'Green AI'; Sustainable Tropical Data Centre Testbed.  [confianza: MEDIA · PRELIM]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1112,13 +1118,13 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>No se halló consulta ciudadana en la elaboración de NAIS 2.0 (sí en el MGF GenAI, otro instrumento) → 1.  [confianza: MEDIA · NO ENCONTRADO]
-Nota matriz: PT: consulta pública con resultados</t>
+          <t>No se halló consulta ciudadana en la elaboración de NAIS 2.0 (sí en el MGF GenAI, otro instrumento) → 1.  [confianza: MEDIA · NO ENCONTRADO]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://www.imda.gov.sg</t>
+          <t>https://www.imda.gov.sg
+https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1151,13 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Elaboración: Gob (SNDGG/MDDI) + industria + investigación (Gob+2).  [confianza: MEDIA · PRELIM]
-Nota matriz: PT: Gob+4</t>
+          <t>Elaboración: Gob (SNDGG/MDDI) + industria + investigación (Gob+2).  [confianza: MEDIA · PRELIM]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>https://file.go.gov.sg/nais2023.pdf
+https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1189,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
+          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+https://aiverifyfoundation.sg/</t>
         </is>
       </c>
     </row>
@@ -1210,8 +1217,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>&gt;1 institución: SNDGG, IMDA, AISG, A*STAR, PDPC, AI Verify Fdn y NAIC (PM, feb-2026).  [confianza: ALTA]
-Nota matriz: ES: SEDIA+AESIA · DE: 3 min+PLS+BNetzA · PT: AMA+FCT+ANACOM</t>
+          <t>&gt;1 institución: SNDGG, IMDA, AISG, A*STAR, PDPC, AI Verify Fdn y NAIC (PM, feb-2026).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1283,13 +1289,13 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Participante (P-member) en SC 42.  [confianza: ALTA]
-Nota matriz: EE: no figura (verificar) · PT: Observador</t>
+          <t>Participante (P-member) en SC 42.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/6794475.html?view=participation</t>
+          <t>https://www.iso.org/committee/6794475.html?view=participation
+https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
         </is>
       </c>
     </row>
@@ -1316,8 +1322,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Participante (P-member) en SC 27.  [confianza: ALTA]
-Nota matriz: PT: Observador</t>
+          <t>Participante (P-member) en SC 27.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1349,14 +1354,13 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>OECD AI Principles + GPAI + ASEAN (lidera WG) + UNESCO ref. + Singapore Consensus 2025 = 2+.  [confianza: ALTA]
-Nota matriz: GPAI: miembros DE/ES; EE/SG/PT no individual</t>
+          <t>OECD AI Principles + GPAI + ASEAN (lidera WG) + UNESCO ref. + Singapore Consensus 2025 = 2+.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
           <t>https://oecd.ai/en/ai-principles
-https://asean.org/</t>
+https://asean.org/wp-content/uploads/2024/02/ASEAN-Guide-on-AI-Governance-and-Ethics_beautified_201223_v2.pdf</t>
         </is>
       </c>
     </row>
@@ -1390,13 +1394,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>No tiene ley dura de IA; gobierna por soft law (MGF 2019/20, MGF GenAI 2024, Agentic 2026) → 1. (No es debilidad: marco voluntario muy maduro.)  [confianza: ALTA]
-Nota matriz: UE: EU AI Act (EE/DE/ES/PT). SG: soft law=1. ES/DE: además ley nacional</t>
+          <t>No tiene ley dura de IA; gobierna por soft law (MGF 2019/20, MGF GenAI 2024, Agentic 2026) → 1. (No es debilidad: marco voluntario muy maduro.)  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://www.pdpc.gov.sg
+          <t>https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework
 https://aiverifyfoundation.sg/</t>
         </is>
       </c>
@@ -1456,8 +1459,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>AI Verify; Global AI Assurance Pilot; GenAI Sandbox.  [confianza: ALTA]
-Nota matriz: ES: 1er sandbox UE</t>
+          <t>AI Verify; Global AI Assurance Pilot; GenAI Sandbox.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -1522,8 +1524,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Personal Data Protection Commission (PDPC).  [confianza: ALTA]
-Nota matriz: AKI/PDPC/BfDI/AEPD/CNPD</t>
+          <t>Personal Data Protection Commission (PDPC).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1562,8 +1563,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO por pilar; GCI 2024 = Tier 1 (total ~99,86). Pilares solo en anexo PDF.  [confianza: MANUAL]
-Nota matriz: Solo ES con pilares; resto Tier 1, pilares en anexo PDF</t>
+          <t>NO ENCONTRADO por pilar; GCI 2024 = Tier 1 (total ~99,86). Pilares solo en anexo PDF.  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1728,8 +1728,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO; SG cubierto por GIRAI (score global 53,77). Por área: portal JS/PDF; alt. LIRNEasia Fig.19.  [confianza: MANUAL]
-Nota matriz: Portal JS/PDF → extracción manual</t>
+          <t>NO ENCONTRADO; SG cubierto por GIRAI (score global 53,77). Por área: portal JS/PDF; alt. LIRNEasia Fig.19.  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -1762,8 +1761,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO (portal JS/PDF; alt. LIRNEasia).  [confianza: MANUAL]
-Nota matriz: Idem</t>
+          <t>NO ENCONTRADO (portal JS/PDF; alt. LIRNEasia).  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -1796,8 +1794,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>86,87 (86,8722) en 'Affordable &amp; clean energy', NRI ed. 2025.  [confianza: MEDIA-ALTA]
-Nota matriz: ES: ver página país NRI</t>
+          <t>86,87 (86,8722) en 'Affordable &amp; clean energy', NRI ed. 2025.  [confianza: MEDIA-ALTA]</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -1829,8 +1826,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>4,93 % (2024) / 5,49 % (2025) de generación renovable. Determinístico: 2,94/59,61 TWh = 4,93 %. Hidro 0 %.  [confianza: ALTA]
-Nota matriz: 2024, renovables total. ES/PT/DE: ERNC excl. gran hidro es menor (ver energia_*.md)</t>
+          <t>4,93 % (2024) / 5,49 % (2025) de generación renovable. Determinístico: 2,94/59,61 TWh = 4,93 %. Hidro 0 %.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
@@ -525,7 +525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Compendio exhaustivo de URLs: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
+          <t>Cada URL va etiquetada [oficial] (gobierno, BOE/Diário da República, ISO/ITU, OCDE, dato primario) o [secundaria] (prensa, despacho, agregador). Compendio exhaustivo: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Fuentes y URLs</t>
+          <t>Fuentes y URLs  ([oficial] primaria · [secundaria] corrobora)</t>
         </is>
       </c>
     </row>
@@ -597,9 +597,9 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
-https://file.go.gov.sg/nais2023.pdf
-https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -631,8 +631,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
-https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -664,8 +664,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
-https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-6191</t>
+          <t>[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+[oficial] https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-6191</t>
         </is>
       </c>
     </row>
@@ -697,8 +697,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
-https://file.go.gov.sg/nais2023.pdf</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[oficial] https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
@@ -730,8 +730,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf
-https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -763,8 +763,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -796,8 +796,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework</t>
         </is>
       </c>
     </row>
@@ -829,8 +829,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -862,8 +862,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://aisingapore.org/</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[secundaria] https://aisingapore.org/</t>
         </is>
       </c>
     </row>
@@ -895,8 +895,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.pdpc.gov.sg</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.pdpc.gov.sg</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[oficial] https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
@@ -960,8 +961,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -993,8 +994,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://aisingapore.org/</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[secundaria] https://aisingapore.org/</t>
         </is>
       </c>
     </row>
@@ -1026,8 +1027,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://asean.org/wp-content/uploads/2024/02/ASEAN-Guide-on-AI-Governance-and-Ethics_beautified_201223_v2.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://asean.org/wp-content/uploads/2024/02/ASEAN-Guide-on-AI-Governance-and-Ethics_beautified_201223_v2.pdf</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1060,8 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1093,8 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
@@ -1123,8 +1126,8 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://www.imda.gov.sg
-https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
+          <t>[oficial] https://www.imda.gov.sg
+[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
         </is>
       </c>
     </row>
@@ -1156,8 +1159,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://file.go.gov.sg/nais2023.pdf
-https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -1189,8 +1192,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
-https://aiverifyfoundation.sg/</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[secundaria] https://aiverifyfoundation.sg/</t>
         </is>
       </c>
     </row>
@@ -1222,8 +1225,8 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
-https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1258,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
+          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
         </is>
       </c>
     </row>
@@ -1294,8 +1298,8 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/6794475.html?view=participation
-https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
+          <t>[oficial] https://www.iso.org/committee/6794475.html?view=participation
+[secundaria] https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1331,8 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/45306.html?view=participation</t>
+          <t>[oficial] https://www.iso.org/committee/45306.html?view=participation
+[secundaria] https://en.wikipedia.org/wiki/ISO/IEC_JTC_1/SC_27</t>
         </is>
       </c>
     </row>
@@ -1359,8 +1364,8 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/ai-principles
-https://asean.org/wp-content/uploads/2024/02/ASEAN-Guide-on-AI-Governance-and-Ethics_beautified_201223_v2.pdf</t>
+          <t>[oficial] https://oecd.ai/en/ai-principles
+[oficial] https://asean.org/wp-content/uploads/2024/02/ASEAN-Guide-on-AI-Governance-and-Ethics_beautified_201223_v2.pdf</t>
         </is>
       </c>
     </row>
@@ -1399,8 +1404,8 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework
-https://aiverifyfoundation.sg/</t>
+          <t>[oficial] https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework
+[secundaria] https://aiverifyfoundation.sg/</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1437,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
+          <t>[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf
+[secundaria] https://aiverifyfoundation.sg/</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1470,8 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://aiverifyfoundation.sg/</t>
+          <t>[secundaria] https://aiverifyfoundation.sg/
+[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
         </is>
       </c>
     </row>
@@ -1496,8 +1503,8 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=SG
-https://sso.agc.gov.sg/Act/PDPA2012</t>
+          <t>[oficial] https://sso.agc.gov.sg/Act/PDPA2012
+[secundaria] https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=SG</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1536,8 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.pdpc.gov.sg</t>
+          <t>[oficial] https://www.pdpc.gov.sg
+[secundaria] https://www.dlapiperdataprotection.com/?t=authority&amp;c=SG</t>
         </is>
       </c>
     </row>
@@ -1568,8 +1576,8 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1601,8 +1609,8 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1634,8 +1642,8 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1667,8 +1675,8 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1700,8 +1708,8 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1733,8 +1741,8 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai
-https://lirneasia.net/wp-content/uploads/2025/03/Draft-Version-for-Review_GIRAI-Report_LIRNEasia_20-March-2025.pdf</t>
+          <t>[oficial] https://www.global-index.ai
+[secundaria] https://lirneasia.net/wp-content/uploads/2025/03/Draft-Version-for-Review_GIRAI-Report_LIRNEasia_20-March-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -1766,8 +1774,8 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai
-https://lirneasia.net/wp-content/uploads/2025/03/Draft-Version-for-Review_GIRAI-Report_LIRNEasia_20-March-2025.pdf</t>
+          <t>[oficial] https://www.global-index.ai
+[secundaria] https://lirneasia.net/wp-content/uploads/2025/03/Draft-Version-for-Review_GIRAI-Report_LIRNEasia_20-March-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1807,8 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>https://networkreadinessindex.org/country/singapore/</t>
+          <t>[oficial] https://networkreadinessindex.org/country/singapore/
+[oficial] https://download.networkreadinessindex.org/reports/countries/2025/singapore.pdf</t>
         </is>
       </c>
     </row>
@@ -1831,8 +1840,8 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
+[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1835,13 +1835,13 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>4,93 % (2024) / 5,49 % (2025) de generación renovable. Determinístico: 2,94/59,61 TWh = 4,93 %. Hidro 0 %.  [confianza: ALTA]</t>
+          <t>Energía limpia 2025 = 5,49 % (renovables 5,49 % + nuclear 0; Bio+Solar, sin hidro). EMBER, determinístico (3,30/60,15 TWh). A confirmar con CENIA.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://ember-energy.org/data/electricity-data-explorer/
+[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_SG_Singapur_ILIA2026.xlsx
@@ -47,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,11 +67,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,9 +122,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -626,13 +618,13 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>NAIS 2.0 = dic-2023; el Update de may-2026 (10 prioridades refrescadas) se cuenta como estrategia vigente nueva (decisión del operador 2026-06-16) → tramo 2024-25.  [confianza: ALTA · decisión operador]</t>
+          <t>Estrategia vigente: el Update 2026 (este PDF, 'Refreshed Priorities/Enablers') refresca NAIS 2.0 (2023); decisión del operador: cuenta como estrategia vigente nueva → tramo 2024-25.  [confianza: ALTA · decisión operador]</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
-[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
+[oficial] https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
@@ -680,9 +672,9 @@
           <t>Mecanismos de evaluación</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -692,313 +684,313 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Supervisión inter-agencias + métricas + NAIC. Sin texto primario íntegro → PRELIM.  [confianza: MEDIA · PRELIM]</t>
+          <t>Validado: NAIS se revisa periódicamente (1.0 2019 → 2.0 2023 → Update 2026, que evalúa el progreso vs. NAIS 2.0) + 'committed to continually reviewing our actions' (Update p.7) + métricas de proyecto. → 3.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+[oficial] https://file.go.gov.sg/nais2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>¿Presupuesto asignado a la estrategia? 1 No menciona · 2 Menciona asignación · 3 Monto especificado.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>'More than S$1 billion' en 5 años.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf
+[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Hoja de ruta</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>¿Plan de acción / hoja de ruta? 1 No · 2 Menciona plan · 3 Plan especificado.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>3 sistemas, 10 enablers y 15 Acciones.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Ética y gobernanza</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Ética y gobernanza.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>'Trusted &amp; responsible AI'; Model AI Governance Framework + AI Verify.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Infraestructura y tecnología</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Infraestructura y tecnología.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Sistema 'Infrastructure'; cómputo.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Desarrollo de capacidades</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Desarrollo de capacidades.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Sistema 'Talent'; AI Singapore.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[secundaria] https://aisingapore.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Datos</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Datos.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Enabler de datos; PDPC.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.pdpc.gov.sg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Gobierno digital</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Gobierno digital.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Smart Nation / Digital Government.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
 [oficial] https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Presupuesto</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>¿Presupuesto asignado a la estrategia? 1 No menciona · 2 Menciona asignación · 3 Monto especificado.</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>'More than S$1 billion' en 5 años.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://www.sgpc.gov.sg/api/file/getfile/Press%20Release_NAIS%202_0%20and%20SCAI_4%20Dec.pdf
-[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Hoja de ruta</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>¿Plan de acción / hoja de ruta? 1 No · 2 Menciona plan · 3 Plan especificado.</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>3 sistemas, 10 enablers y 15 Acciones.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: Industria y emprendimiento</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Industria y emprendimiento.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Enabler de industria; LLM nacional.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://file.go.gov.sg/nais2023.pdf
 [oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Ética y gobernanza</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Tópico: I+D</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Ética y gobernanza.</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>'Trusted &amp; responsible AI'; Model AI Governance Framework + AI Verify.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[oficial] https://www.pdpc.gov.sg/help-and-resources/2020/01/model-ai-governance-framework</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Infraestructura y tecnología</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Infraestructura y tecnología.</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Sistema 'Infrastructure'; cómputo.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Desarrollo de capacidades</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Desarrollo de capacidades.</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Sistema 'Talent'; AI Singapore.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: I+D.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Enabler de investigación; A*STAR/AISG.  [confianza: ALTA]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://file.go.gov.sg/nais2023.pdf
 [secundaria] https://aisingapore.org/</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Datos</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Datos.</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Enabler de datos; PDPC.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[oficial] https://www.pdpc.gov.sg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Gobierno digital</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Gobierno digital.</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Smart Nation / Digital Government.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/
-[oficial] https://file.go.gov.sg/nais2023.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: Industria y emprendimiento</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: Industria y emprendimiento.</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Enabler de industria; LLM nacional.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Tópico: I+D</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Tópico de la estrategia (binario 0/1): el aspecto está recogido y con plan de acción. Aquí: I+D.</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Enabler de investigación; A*STAR/AISG.  [confianza: ALTA]</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[secundaria] https://aisingapore.org/</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1055,12 +1047,13 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>NO se halló componente de género con plan → 0.  [confianza: MEDIA · NO ENCONTRADO]</t>
+          <t>Género NO es eje con plan → 0. Búsqueda en los 3 PDF: 'gender'/'women' no aparecen como tema; 'diversity' = diversidad lingüística/industria; 'inclusive growth' = capacidades amplias del trabajador (Update p.26), no enfoque de género.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
 [oficial] https://www.smartnation.gov.sg/initiatives/national-ai-strategy/</t>
         </is>
       </c>
@@ -1076,9 +1069,9 @@
           <t>Tópico: Sostenibilidad</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1088,12 +1081,13 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>'Green AI'; Sustainable Tropical Data Centre Testbed.  [confianza: MEDIA · PRELIM]</t>
+          <t>Validado: sostenibilidad como prioridad refrescada — 'Advance resource-efficient AI ... in line with Singapore's sustainability goals' (Update p.3/33) + Green Data Centre Roadmap (p.31) + tema 'Resource-Efficient AI' (NAIS 2.0 p.20). → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+          <t>[oficial] https://www.mddi.gov.sg/newsroom/update-to-singapore-s-national-ai-strategy--refreshed-priorities-to-harness-ai-for-the-public-good-factsheet/
+[oficial] https://file.go.gov.sg/nais2023.pdf
 [oficial] https://www.smartnation.gov.sg/files/publications/infographic_nais2_0.pdf</t>
         </is>
       </c>
@@ -1109,9 +1103,9 @@
           <t>Particip. ciudadana elaboración</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1121,13 +1115,13 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>No se halló consulta ciudadana en la elaboración de NAIS 2.0 (sí en el MGF GenAI, otro instrumento) → 1.  [confianza: MEDIA · NO ENCONTRADO]</t>
+          <t>Sin mecanismo de participación CIUDADANA en la elaboración: la consulta fue 'in close consultation with AI ecosystem representatives' (NAIS 2.0 p.45) — representantes del ecosistema (cuentan en 121), no público general. Hay consultas públicas para guías puntuales (MGF GenAI, Securing AI), no para la estrategia. → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://www.imda.gov.sg
-[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[oficial] https://www.imda.gov.sg</t>
         </is>
       </c>
     </row>
@@ -1142,9 +1136,9 @@
           <t>Multistakeholder elaboración</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1154,13 +1148,12 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Elaboración: Gob (SNDGG/MDDI) + industria + investigación (Gob+2).  [confianza: MEDIA · PRELIM]</t>
+          <t>Sectores en la ELABORACIÓN: Gob + INDUSTRIA + ACADEMIA + NON-PROFIT. SCAI reunió '40 ... experts from academia, non-profit, industry and government' (NAIS 2.0 p.33); RAISE.SG 'academia, industry, and non-profit' (p.46). → Gob+3 = 4. (Posible 5 con internacional/público.)  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
-[oficial] https://www.mddi.gov.sg/newsroom/04122023/</t>
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf</t>
         </is>
       </c>
     </row>
@@ -1175,9 +1168,9 @@
           <t>Multistakeholder implementación</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>4 (PRELIM)</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1187,7 +1180,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Implementación: Gob + industria + academia + AI Verify Foundation (Gob+3).  [confianza: MEDIA · PRELIM]</t>
+          <t>Sectores en la IMPLEMENTACIÓN: 'A Whole-of-Nation Movement' (NAIS 2.0 p.67); Tripartite Jobs Council = Gob + NTUC (trabajadores) + Employers Federation (Update p.26); AI Verify Foundation (non-profit/comunidad global); co-desarrollo con industria (Update p.18). → Gob+3 = 4 (defendible 5 con internacional/trabajadores).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1399,7 +1392,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>No tiene ley dura de IA; gobierna por soft law (MGF 2019/20, MGF GenAI 2024, Agentic 2026) → 1. (No es debilidad: marco voluntario muy maduro.)  [confianza: ALTA]</t>
+          <t>No tiene ley dura de IA; soft law: Model AI Governance Frameworks (2019; GenAI 2024; Agentic 2026, 1º del mundo, Update p.36); 'lighter-touch frameworks' (p.41). → 1. (No es debilidad: marco voluntario muy maduro.)  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1420,9 +1413,9 @@
           <t>Clasificación de riesgo</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1432,12 +1425,13 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>La clasificación de riesgo está en el marco voluntario (MGF GenAI: 9 dimensiones), no en una ley.  [confianza: MEDIA · PRELIM]</t>
+          <t>Validado: enfoque por riesgo escalonado — 'interventions that are risk-based, tiered, and adapted for specific ... sectors' (NAIS 2.0 p.59); 'balanced, risk-based approach ... for higher-risk use cases' (Update p.17). En marco voluntario, no ley. → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf
+          <t>[oficial] https://file.go.gov.sg/nais2023.pdf
+[secundaria] https://aiverifyfoundation.sg/wp-content/uploads/2024/06/Model-AI-Governance-Framework-for-Generative-AI-19-June-2024.pdf
 [secundaria] https://aiverifyfoundation.sg/</t>
         </is>
       </c>
@@ -1465,7 +1459,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>AI Verify; Global AI Assurance Pilot; GenAI Sandbox.  [confianza: ALTA]</t>
+          <t>Validado: AI Verify + Global AI Assurance Sandbox (Update p.37) + PET Sandbox (9 casos en finanzas/salud/publicidad, p.34). → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -1559,7 +1553,7 @@
           <t>Ciberseguridad — Legal</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>PEND</t>
         </is>
@@ -1592,7 +1586,7 @@
           <t>Ciberseguridad — Técnico</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>PEND</t>
         </is>
@@ -1625,7 +1619,7 @@
           <t>Ciberseguridad — Organizacional</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>PEND</t>
         </is>
@@ -1658,7 +1652,7 @@
           <t>Ciberseguridad — Desarrollo de capacidades</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>PEND</t>
         </is>
@@ -1691,7 +1685,7 @@
           <t>Ciberseguridad — Cooperación</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>PEND</t>
         </is>
@@ -1724,7 +1718,7 @@
           <t>GIRAI — Protección de datos y privacidad</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
@@ -1757,7 +1751,7 @@
           <t>GIRAI — Seguridad, precisión y confiabilidad</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
